--- a/architectures and decision enablers/architecture decision enabler/ai-vectordb-vendor-evaluation/AI_Vector_DB_Evaluator.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/ai-vectordb-vendor-evaluation/AI_Vector_DB_Evaluator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\architecture decision enabler\ai-vectordb-vendor-evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98055095-094F-47AD-8E76-E262F6BEC9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE23F1D3-8B35-45DF-82B2-A6385B941208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{11FE6716-00EB-4A8F-BF84-8278D6931338}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{11FE6716-00EB-4A8F-BF84-8278D6931338}"/>
   </bookViews>
   <sheets>
     <sheet name="Platform_DB" sheetId="1" r:id="rId1"/>
